--- a/Data/EXCEL/Transfer/salemon/20240711/6648-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6648-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EC35797-7F04-4566-9F9E-27AEDF83FDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E05AE7-8FB6-4D05-8B4A-7EBBA81D24C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{5F839D5C-BF60-4FC2-AFD4-01462F659877}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{D97D7044-6CD7-4434-AC3B-42D14722EC8C}"/>
   </bookViews>
   <sheets>
     <sheet name="6648-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,26 +1261,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED0103D-9539-43B1-9C3F-3A0195B67FA9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A164C8-9237-49D2-8459-66DB9C27EF30}">
   <dimension ref="A1:Q177"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1307,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1389,7 +1389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1428,7 +1428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>-26.4</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>-26.2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>-21.6</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>-42.1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>-41.7</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>-41.9</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>-43.4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>-51.4</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>-52.9</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>-65.599999999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>-66.400000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>-64</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>-47.7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>-17.3</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>152.9</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>41.4</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>96.9</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>126.2</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>544.29999999999995</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>491.2</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>311.60000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>83.3</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>-37</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>-13.8</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>-9.09</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>-14.9</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>-28.7</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>-31.6</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>-18.2</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>-52.4</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>39.799999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>161.80000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>285.60000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>276.60000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>254.2</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>186.8</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>127.2</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>-2.08</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>-58</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>-69.5</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>-7.48</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>-11.7</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>170.2</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>146.4</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>293.8</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>883.3</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>883.3</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>-33.299999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>-38</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>-51.7</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>-54</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>-55.2</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>-83.4</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>-82.2</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>-77.7</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>-83.5</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5456,7 +5456,7 @@
         <v>-6.4</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>294.60000000000002</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>479.9</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>760.7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>714.4</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>657.4</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5880,447 +5880,447 @@
         <v>566.20000000000005</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>42917</v>
       </c>
